--- a/product_upload/packages/30/file.xlsx
+++ b/product_upload/packages/30/file.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,7 +596,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -645,6 +645,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -669,7 +674,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -836,6 +841,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>0.22% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-2E51FFAD6232</t>
         </is>
       </c>
@@ -859,7 +869,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1022,6 +1032,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>0.22% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-CB63E3052821</t>
         </is>
       </c>
@@ -1045,7 +1060,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1212,6 +1227,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>0.15% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-9DF080979BC7</t>
         </is>
       </c>
@@ -1235,7 +1255,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1398,6 +1418,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>0.15% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-262FF0C3FC08</t>
         </is>
       </c>
@@ -1421,7 +1446,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1584,6 +1609,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>0.075% POTASSIUM CHLORIDE in 5% DEXTROSE and 0.45% SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-264F2C8254CD</t>
         </is>
       </c>
@@ -1607,7 +1637,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1778,6 +1808,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>ARPENIA 15 mg ORODISPERSIBLE TABLET</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-64BD44831A68</t>
         </is>
       </c>
@@ -1801,7 +1836,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1968,6 +2003,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>PRINCEOXIN 250 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-E1D49AF2247B</t>
         </is>
       </c>
@@ -1991,7 +2031,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2158,6 +2198,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>PREGA 50 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-34F15A8BEB06</t>
         </is>
       </c>
@@ -2181,7 +2226,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2348,6 +2393,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>PREGA 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-F7CDFEB478DC</t>
         </is>
       </c>
@@ -2371,7 +2421,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2538,6 +2588,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>PREGA 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-B8FE5B9E86DB</t>
         </is>
       </c>
@@ -2561,7 +2616,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2728,6 +2783,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>PREGA 150 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-9A1EA1D22D9C</t>
         </is>
       </c>
@@ -2751,7 +2811,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2914,6 +2974,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>PREGA 150 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-5139845CD3AA</t>
         </is>
       </c>
@@ -2937,7 +3002,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3100,6 +3165,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>PREGA 300 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-D1F72DD16C5A</t>
         </is>
       </c>
@@ -3123,7 +3193,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3290,6 +3360,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>PREGA 300 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-2FC9136BE924</t>
         </is>
       </c>
@@ -3313,7 +3388,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3480,6 +3555,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>TAPCLOB 5MG/5ML ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-4302695E989C</t>
         </is>
       </c>
@@ -3503,7 +3583,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3674,6 +3754,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>TAPCLOB 10MG/5ML ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-881E1881FE1B</t>
         </is>
       </c>
@@ -3697,7 +3782,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3860,6 +3945,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>ESSERA 50 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-B3FFD31C3F00</t>
         </is>
       </c>
@@ -3883,7 +3973,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4050,6 +4140,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>ESSERA 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-D7D25DFA345C</t>
         </is>
       </c>
@@ -4073,7 +4168,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4236,6 +4331,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>PRINCEOXIN 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-45C64F6793F6</t>
         </is>
       </c>
@@ -4259,7 +4359,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4426,6 +4526,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>Risilud 0.05% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-288357A5B11C</t>
         </is>
       </c>
@@ -4449,7 +4554,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4612,6 +4717,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>LOCASONE S OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-A4BCF28E01BB</t>
         </is>
       </c>
@@ -4635,7 +4745,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4798,6 +4908,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>LOCASONE S OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-DD98521B3DF3</t>
         </is>
       </c>
@@ -4821,7 +4936,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4984,6 +5099,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>LOCASONE S OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-F55D67624343</t>
         </is>
       </c>
@@ -5007,7 +5127,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5182,6 +5302,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>ESSENTIAL D-3 50000 IU CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-40EF35AB5F91</t>
         </is>
       </c>
@@ -5205,7 +5330,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5380,6 +5505,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>TREZOL 2.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-B0351A3D7604</t>
         </is>
       </c>
@@ -5403,7 +5533,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5570,6 +5700,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>LAMIRA 25 mg TABLET</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-B660562F2815</t>
         </is>
       </c>
@@ -5593,7 +5728,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5764,6 +5899,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>LAMIRA 50 mg TABLET</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-157DF24216BE</t>
         </is>
       </c>
@@ -5787,7 +5927,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5958,6 +6098,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>LAMIRA 100 mg TABLET</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-9984CC2735B5</t>
         </is>
       </c>
@@ -5981,7 +6126,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6144,6 +6289,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>LOCASONE S OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-01538C7F3086</t>
         </is>
       </c>
@@ -6167,7 +6317,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6338,6 +6488,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>ARPENIA 10 mg ORODISPERSIBLE TABLET</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-84017912FA63</t>
         </is>
       </c>
@@ -6361,7 +6516,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6524,6 +6679,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>TRANDATE TAB 200 MG.</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-FB862BDC39E3</t>
         </is>
       </c>
@@ -6547,7 +6707,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6710,6 +6870,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>SYNACTHEN DEPOT</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-8D506961E49B</t>
         </is>
       </c>
@@ -6733,7 +6898,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6900,6 +7065,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>LEVOZIN 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-DAA12E58BD87</t>
         </is>
       </c>
@@ -6923,7 +7093,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7090,6 +7260,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>RIDON 1 MG/ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-844EF5B61D4B</t>
         </is>
       </c>
@@ -7113,7 +7288,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7280,6 +7455,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>MOXICAN 400 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-610D2394AACF</t>
         </is>
       </c>
@@ -7303,7 +7483,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7470,6 +7650,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>CUREAML 500 mg Capsules</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-8577F14E35B4</t>
         </is>
       </c>
@@ -7493,7 +7678,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7660,6 +7845,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>DANOVAR</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-6122D4843B20</t>
         </is>
       </c>
@@ -7683,7 +7873,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7854,6 +8044,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>DIOSTAR PLUS</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-882A243F6D54</t>
         </is>
       </c>
@@ -7877,7 +8072,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8048,6 +8243,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>DIOSTAR PLUS</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-D9DE2724C64A</t>
         </is>
       </c>
@@ -8071,7 +8271,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8238,6 +8438,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>EMDITIL 500MG Film-coated TABLET</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-0BDBACEF11A1</t>
         </is>
       </c>
@@ -8261,7 +8466,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8432,6 +8637,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>ELTROXIN 0.05MG TAB</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-FF98B98685E9</t>
         </is>
       </c>
@@ -8455,7 +8665,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8622,6 +8832,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>ELTROXIN 0.1MG TAB</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-AB1D559351B7</t>
         </is>
       </c>
@@ -8645,7 +8860,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8816,6 +9031,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>PURINETHOL 50MG TAB</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-E8C90D38C1B3</t>
         </is>
       </c>
@@ -8839,7 +9059,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9002,6 +9222,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>TRANDATE 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-F1F2AEBD5696</t>
         </is>
       </c>
@@ -9025,7 +9250,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9192,6 +9417,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>DIOSTAR PLUS</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-C2EF7E886F41</t>
         </is>
       </c>
@@ -9215,7 +9445,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9390,6 +9620,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>ATORLIP 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-B25626031FF5</t>
         </is>
       </c>
@@ -9413,7 +9648,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9592,6 +9827,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>ATORLIP 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-0A3216C19B0C</t>
         </is>
       </c>
@@ -9615,7 +9855,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9786,6 +10026,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>ACUVAIL ophthalmic solution</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-9795D6284412</t>
         </is>
       </c>
@@ -9809,7 +10054,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9976,6 +10221,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>ADAZIO 25 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-465AB3EA82E0</t>
         </is>
       </c>
@@ -9999,7 +10249,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10170,6 +10420,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>ADAZIO 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-53D0E5848134</t>
         </is>
       </c>
@@ -10193,7 +10448,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10364,6 +10619,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>ADAZIO 200 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-D1BA99D8304C</t>
         </is>
       </c>
@@ -10387,7 +10647,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10558,6 +10818,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>ADAZIO 300 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-2EC9D19B4F07</t>
         </is>
       </c>
@@ -10581,7 +10846,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10744,6 +11009,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>BRONCHOFAST 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-3283FAA783F5</t>
         </is>
       </c>
@@ -10767,7 +11037,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10934,6 +11204,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>AZERA 100 mg enteric-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-AF7E0CE100B1</t>
         </is>
       </c>
@@ -10957,7 +11232,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11132,6 +11407,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>SORTIVA H 100/12.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-A714F5EFAEBE</t>
         </is>
       </c>
@@ -11155,7 +11435,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11330,6 +11610,11 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>JURNISTA 8 mg prolonged-release tablet</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-43FB5E46EC0F</t>
         </is>
       </c>
@@ -11353,7 +11638,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11520,6 +11805,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>JURNISTA 16 mg prolonged-release tablet</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-688F721BAE97</t>
         </is>
       </c>
@@ -11543,7 +11833,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11710,6 +12000,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>JURNISTA 32 mg prolonged-release tablet</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-C699CEAB276D</t>
         </is>
       </c>
@@ -11733,7 +12028,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11904,6 +12199,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>VIVARO 100 IU/ml pre-filled pen, disposable</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-6B0BBDE2F650</t>
         </is>
       </c>
@@ -11927,7 +12227,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12090,6 +12390,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>VASTALIP 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-6395745FF9F0</t>
         </is>
       </c>
@@ -12113,7 +12418,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12280,6 +12585,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>VASTALIP 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-96DAFA23DBE8</t>
         </is>
       </c>
@@ -12303,7 +12613,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12482,6 +12792,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>ATORLIP 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-233F6720AE8D</t>
         </is>
       </c>
@@ -12505,7 +12820,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12676,6 +12991,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>RENVELA 2.4 g powder for oral suspension</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-A9CBEBFAF882</t>
         </is>
       </c>
@@ -12699,7 +13019,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12866,6 +13186,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>SEVORANE INHAL.ANESTHESIA Plastic BOTTLE</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-19E1E4C46D83</t>
         </is>
       </c>
@@ -12889,7 +13214,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -13060,6 +13385,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>SEVORANE INHAL.ANESTHESIA aluminum BOTTLE</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-3ECE4EBD16A0</t>
         </is>
       </c>
@@ -13083,7 +13413,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13266,6 +13596,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>HUMIRA 40MG/0.4ML PRE- FILLED SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-5C6053838EFA</t>
         </is>
       </c>
@@ -13289,7 +13624,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13464,6 +13799,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>SOLPADEINE CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-3777EB8A3874</t>
         </is>
       </c>
@@ -13487,7 +13827,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13650,6 +13990,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>VASTALIP 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-DE99227D938B</t>
         </is>
       </c>
@@ -13673,7 +14018,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13832,6 +14177,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>GRACIAL TABLET</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-8E8065E04734</t>
         </is>
       </c>
@@ -13855,7 +14205,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -14022,6 +14372,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>METHADONE MARTINDALE PHARMA 2 mg/ml oral solution</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-80060B3982CB</t>
         </is>
       </c>
@@ -14045,7 +14400,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14208,6 +14563,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>METHADONE MARTINDALE PHARMA 2 mg/ml oral solution</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-D666F6BAB29B</t>
         </is>
       </c>
@@ -14231,7 +14591,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14394,6 +14754,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>SETININ 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-A7933B2DF2E9</t>
         </is>
       </c>
@@ -14417,7 +14782,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14584,6 +14949,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>G-PRIDE 1 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-301A28EDA67B</t>
         </is>
       </c>
@@ -14607,7 +14977,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14770,6 +15140,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>G-PRIDE 2 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-643B90B0B78C</t>
         </is>
       </c>
@@ -14793,7 +15168,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14972,6 +15347,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>BIODAL 50000 iu tablet</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-09A169FB2BA9</t>
         </is>
       </c>
@@ -14995,7 +15375,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15170,6 +15550,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>AVOQUIN cream</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-CAA918CA623A</t>
         </is>
       </c>
@@ -15193,7 +15578,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15356,6 +15741,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>BLOCAL 5 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-658528CC5115</t>
         </is>
       </c>
@@ -15379,7 +15769,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15554,6 +15944,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>DEMENT 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-A7A75072B2F1</t>
         </is>
       </c>
@@ -15577,7 +15972,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15748,6 +16143,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>BRONCHOVENT 5mg/ml nebuliser solution</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-138402B59E2E</t>
         </is>
       </c>
@@ -15771,7 +16171,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15942,6 +16342,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>NATURAL E 400 softgel capsule</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-B490F87ACBF9</t>
         </is>
       </c>
@@ -15965,7 +16370,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16132,6 +16537,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>IROVEL 150 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-3021A65E447C</t>
         </is>
       </c>
@@ -16155,7 +16565,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16326,6 +16736,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>IROVEL 300 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-ED4FD6CD7284</t>
         </is>
       </c>
@@ -16349,7 +16764,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16520,6 +16935,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>VIOTOPIC 0.03% ointment</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-4780CF3A88DC</t>
         </is>
       </c>
@@ -16543,7 +16963,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16714,6 +17134,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>VIOTOPIC 0.1% ointment</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-DAA365904BE7</t>
         </is>
       </c>
@@ -16737,7 +17162,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16904,6 +17329,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>BALANCED ELECTROLYTES pH 7.4 solution for infusion</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-B93C3B59C118</t>
         </is>
       </c>
@@ -16927,7 +17357,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -17086,6 +17516,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>BALANCED ELECTROLYTES pH 7.4 solution for infusion</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-CCBF74366A82</t>
         </is>
       </c>
@@ -17109,7 +17544,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17272,6 +17707,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>BALANCED ELECTROLYTES pH 7.4 solution for infusion</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-D67AAE60FB44</t>
         </is>
       </c>
@@ -17295,7 +17735,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17466,6 +17906,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>CoDICERAN 16/12.5 film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-9B1AB2385020</t>
         </is>
       </c>
@@ -17489,7 +17934,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17656,6 +18101,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>HAVRIX</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-EC21CD109DBA</t>
         </is>
       </c>
@@ -17679,7 +18129,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17842,6 +18292,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>OLANA 10 mg orodispersible tablet</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-ECAF71F212D9</t>
         </is>
       </c>
@@ -17865,7 +18320,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -18028,6 +18483,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>SETININ 200 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-F2FFB88A8356</t>
         </is>
       </c>
@@ -18051,7 +18511,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18214,6 +18674,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>SETININ 300 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-B65FC508F4BB</t>
         </is>
       </c>
@@ -18237,7 +18702,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18412,6 +18877,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>BRONCAST 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-A58D45C8E0B4</t>
         </is>
       </c>
@@ -18435,7 +18905,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18606,6 +19076,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>BRONCAST 5 mg chewable tablet</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-270775EA8699</t>
         </is>
       </c>
@@ -18629,7 +19104,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18800,6 +19275,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>LEVOFLOXACIN Sandoz 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-980FA846D210</t>
         </is>
       </c>
@@ -18823,7 +19303,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18994,6 +19474,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>CELEBREX 400 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-C3E7DF29CF20</t>
         </is>
       </c>
@@ -19017,7 +19502,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19192,6 +19677,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>BROFIX 0.09% eye drops solution</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-F1E1A0496405</t>
         </is>
       </c>
@@ -19215,7 +19705,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19386,6 +19876,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>CIPRALEX 10 MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-37912D64F81E</t>
         </is>
       </c>
@@ -19409,7 +19904,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19576,6 +20071,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>CIPRALEX 10 MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-FF61734F1DF0</t>
         </is>
       </c>
@@ -19599,7 +20099,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19773,6 +20273,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>CIPRALEX 20MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-63636B810CCA</t>
         </is>
@@ -19789,7 +20294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19835,100 +20340,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19960,7 +20470,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19975,92 +20485,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-27111</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>152.06</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>242</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20092,7 +20607,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -20107,92 +20622,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-83496</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>186.45</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>243</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20224,7 +20744,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20239,92 +20759,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-48523</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>16.19</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>244</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20356,7 +20881,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20371,92 +20896,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-11625</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>379.43</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>245</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20488,7 +21018,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20503,92 +21033,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-88867</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>491.89</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>246</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20620,7 +21155,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20635,92 +21170,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-68507</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>482.22</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>247</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20752,7 +21292,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20767,92 +21307,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-87169</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>310.39</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>248</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20884,7 +21429,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20899,92 +21444,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-12469</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>394.7</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>249</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21016,7 +21566,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -21031,92 +21581,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-12101</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>454.02</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>250</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21148,7 +21703,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -21163,92 +21718,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-48025</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>497.39</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>251</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21280,7 +21840,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21295,92 +21855,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-54979</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>166.1</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>252</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21397,7 +21962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21503,6 +22068,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21538,7 +22113,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21603,6 +22178,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-86C9B5D60E7A</t>
         </is>
@@ -21639,7 +22224,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21704,6 +22289,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-9EF0235C4100</t>
         </is>
@@ -21740,7 +22335,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21805,6 +22400,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-EC81E3B0193E</t>
         </is>
@@ -21841,7 +22446,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21906,6 +22511,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-342B48F4AA35</t>
         </is>
@@ -21942,7 +22557,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -22007,6 +22622,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-4AA56BE3BF4D</t>
         </is>
@@ -22043,7 +22668,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22108,6 +22733,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-82A802C0B8F6</t>
         </is>
@@ -22144,7 +22779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22209,6 +22844,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-86FD0504F289</t>
         </is>
@@ -22245,7 +22890,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22310,6 +22955,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-F5CDE34768D3</t>
         </is>
@@ -22346,7 +23001,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22411,6 +23066,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-50247B87831C</t>
         </is>
@@ -22447,7 +23112,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22512,6 +23177,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-C4D1C1A16F0C</t>
         </is>
@@ -22548,7 +23223,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22613,6 +23288,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-ACEEA7ECA7BD</t>
         </is>
@@ -22649,7 +23334,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22714,6 +23399,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-DA6A1911C1B1</t>
         </is>
@@ -22750,7 +23445,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22815,6 +23510,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-8F599BCA96ED</t>
         </is>
@@ -22851,7 +23556,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22916,6 +23621,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-BF494B91C53D</t>
         </is>
@@ -22952,7 +23667,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -23017,6 +23732,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-29CB11AB035A</t>
         </is>
@@ -23053,7 +23778,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -23118,6 +23843,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-892F5C7C9A3C</t>
         </is>
@@ -23154,7 +23889,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23219,6 +23954,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-EF9F7E369E7C</t>
         </is>
@@ -23255,7 +24000,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23320,6 +24065,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-5CDF25FFA7B0</t>
         </is>
@@ -23356,7 +24111,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23421,6 +24176,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-48B42B6999BF</t>
         </is>
@@ -23457,7 +24222,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23522,6 +24287,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-0E7EB47A0729</t>
         </is>

--- a/product_upload/packages/30/file.xlsx
+++ b/product_upload/packages/30/file.xlsx
@@ -682,8 +682,16 @@
           <t>9500920872-461-799695038460</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.22% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.22% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
@@ -877,8 +885,16 @@
           <t>5859693635-069-561788033886</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.22% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.22% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1068,8 +1084,16 @@
           <t>4291599784-557-967911154309</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.15% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.15% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1263,8 +1287,16 @@
           <t>9004452765-356-853996617729</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.15% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.15% POTASSIUM CHLORIDE in 0.9% SODIUM CHLORIDE Injection USP detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1454,8 +1486,16 @@
           <t>7754088554-604-003957460166</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.075% POTASSIUM CHLORIDE in 5% DEXTROSE and 0.45% SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.075% POTASSIUM CHLORIDE in 5% DEXTROSE and 0.45% SODIUM CHLORIDE Injection USP detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1844,8 +1884,16 @@
           <t>5971392456-283-128420076984</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PRINCEOXIN 250 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PRINCEOXIN 250 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
@@ -2039,8 +2087,16 @@
           <t>8616064469-019-850739138476</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREGA 50 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PREGA 50 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
@@ -2234,8 +2290,16 @@
           <t>2881999831-422-407533464961</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREGA 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PREGA 75 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
@@ -2429,8 +2493,16 @@
           <t>3537614695-757-693591250741</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREGA 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PREGA 75 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
@@ -2624,8 +2696,16 @@
           <t>6312366232-219-799752968565</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREGA 150 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PREGA 150 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
@@ -2819,8 +2899,16 @@
           <t>4569148639-708-756796256976</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREGA 150 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PREGA 150 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
@@ -3010,8 +3098,16 @@
           <t>7453175195-965-290584048116</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREGA 300 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PREGA 300 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
@@ -3201,8 +3297,16 @@
           <t>0962775298-676-339418051718</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREGA 300 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PREGA 300 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
@@ -3396,8 +3500,16 @@
           <t>5092779684-050-025923442993</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TAPCLOB 5MG/5ML ORAL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TAPCLOB 5MG/5ML ORAL SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
@@ -3790,8 +3902,16 @@
           <t>6771956262-703-474841120808</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESSERA 50 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ESSERA 50 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
@@ -3981,8 +4101,16 @@
           <t>5960678714-055-864086906115</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESSERA 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ESSERA 100 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
@@ -4176,8 +4304,16 @@
           <t>3701758268-274-360745401894</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PRINCEOXIN 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>PRINCEOXIN 500 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
@@ -4367,8 +4503,16 @@
           <t>1102558734-082-190864031704</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Risilud 0.05% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Risilud 0.05% NASAL SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
@@ -4562,8 +4706,16 @@
           <t>3499551713-371-074199518337</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCASONE S OINTMENT</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>LOCASONE S OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
@@ -4753,8 +4905,16 @@
           <t>9224636413-501-191761725773</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCASONE S OINTMENT</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>LOCASONE S OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
@@ -4944,8 +5104,16 @@
           <t>9770518608-399-432205870189</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCASONE S OINTMENT</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>LOCASONE S OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
@@ -5541,8 +5709,16 @@
           <t>3641129226-595-048343305908</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAMIRA 25 mg TABLET</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>LAMIRA 25 mg TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
@@ -6134,8 +6310,16 @@
           <t>9254570064-004-744894036084</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCASONE S OINTMENT</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>LOCASONE S OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>0</t>
@@ -6524,8 +6708,16 @@
           <t>4624505087-487-839390029551</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRANDATE TAB 200 MG.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>TRANDATE TAB 200 MG. detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>0</t>
@@ -6715,8 +6907,16 @@
           <t>2448462962-298-415918622450</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SYNACTHEN DEPOT</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SYNACTHEN DEPOT detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>0</t>
@@ -6906,8 +7106,16 @@
           <t>2912061083-595-949402358799</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVOZIN 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>LEVOZIN 5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>0</t>
@@ -7296,8 +7504,16 @@
           <t>3737499668-574-607254224138</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOXICAN 400 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>MOXICAN 400 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>0</t>
@@ -7686,8 +7902,16 @@
           <t>4684387604-820-197374386388</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DANOVAR</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>DANOVAR detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>0</t>
@@ -7881,8 +8105,16 @@
           <t>6254550765-580-678583481563</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIOSTAR PLUS</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>DIOSTAR PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>0</t>
@@ -8080,8 +8312,16 @@
           <t>2511719041-905-988510253045</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIOSTAR PLUS</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>DIOSTAR PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>0</t>
@@ -8279,8 +8519,16 @@
           <t>8363583461-603-286314050778</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EMDITIL 500MG Film-coated TABLET</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>EMDITIL 500MG Film-coated TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>0</t>
@@ -8673,8 +8921,16 @@
           <t>8520735062-783-521941073899</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ELTROXIN 0.1MG TAB</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ELTROXIN 0.1MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -9067,8 +9323,16 @@
           <t>7433921693-261-760858122510</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRANDATE 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>TRANDATE 100MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>0</t>
@@ -9258,8 +9522,16 @@
           <t>9263301152-116-002885266663</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIOSTAR PLUS</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>DIOSTAR PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>0</t>
@@ -10062,8 +10334,16 @@
           <t>4675259393-204-612526655355</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADAZIO 25 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ADAZIO 25 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>0</t>
@@ -10854,8 +11134,16 @@
           <t>4518700502-673-821824464661</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BRONCHOFAST 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>BRONCHOFAST 10 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>0</t>
@@ -11045,8 +11333,16 @@
           <t>5646905739-523-549896973570</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AZERA 100 mg enteric-coated tablet</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>AZERA 100 mg enteric-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>0</t>
@@ -11841,8 +12137,16 @@
           <t>4010067197-256-453737195979</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JURNISTA 32 mg prolonged-release tablet</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>JURNISTA 32 mg prolonged-release tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>0</t>
@@ -12235,8 +12539,16 @@
           <t>3248835883-875-499391161894</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VASTALIP 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>VASTALIP 40 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>0</t>
@@ -12426,8 +12738,16 @@
           <t>8131828149-507-342756271867</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VASTALIP 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>VASTALIP 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>0</t>
@@ -13027,8 +13347,16 @@
           <t>6815174780-346-932729348315</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEVORANE INHAL.ANESTHESIA Plastic BOTTLE</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>SEVORANE INHAL.ANESTHESIA Plastic BOTTLE detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>ARAB COMPANY FOR PHARMACEUTICAL PRODUCTS (ARABIO)</t>
@@ -13222,8 +13550,16 @@
           <t>9265154906-949-452006598087</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEVORANE INHAL.ANESTHESIA aluminum BOTTLE</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>SEVORANE INHAL.ANESTHESIA aluminum BOTTLE detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>ARAB COMPANY FOR PHARMACEUTICAL PRODUCTS (ARABIO)</t>
@@ -13835,8 +14171,16 @@
           <t>1349563506-918-171741349444</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VASTALIP 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>VASTALIP 10 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>0</t>
@@ -14026,8 +14370,16 @@
           <t>6640164474-422-955928337399</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GRACIAL TABLET</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>GRACIAL TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>0</t>
@@ -14213,8 +14565,16 @@
           <t>2051302638-162-467766869190</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ METHADONE MARTINDALE PHARMA 2 mg/ml oral solution</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>METHADONE MARTINDALE PHARMA 2 mg/ml oral solution detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>0</t>
@@ -14408,8 +14768,16 @@
           <t>6341554480-767-555405450512</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ METHADONE MARTINDALE PHARMA 2 mg/ml oral solution</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>METHADONE MARTINDALE PHARMA 2 mg/ml oral solution detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>0</t>
@@ -14599,8 +14967,16 @@
           <t>3140133350-200-080360535944</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SETININ 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>SETININ 100 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>0</t>
@@ -14790,8 +15166,16 @@
           <t>5300656301-055-895866311057</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ G-PRIDE 1 mg tablet</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>G-PRIDE 1 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>0</t>
@@ -14985,8 +15369,16 @@
           <t>2580326499-666-229650459876</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ G-PRIDE 2 mg tablet</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>G-PRIDE 2 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>0</t>
@@ -15586,8 +15978,16 @@
           <t>0397096126-997-037461500362</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BLOCAL 5 mg capsule</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>BLOCAL 5 mg capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>0</t>
@@ -17170,8 +17570,16 @@
           <t>6398998023-817-516567942914</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BALANCED ELECTROLYTES pH 7.4 solution for infusion</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>BALANCED ELECTROLYTES pH 7.4 solution for infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>0</t>
@@ -17365,8 +17773,16 @@
           <t>3687244016-567-547142649530</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BALANCED ELECTROLYTES pH 7.4 solution for infusion</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>BALANCED ELECTROLYTES pH 7.4 solution for infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>0</t>
@@ -17552,8 +17968,16 @@
           <t>0551093152-288-239047393668</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BALANCED ELECTROLYTES pH 7.4 solution for infusion</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>BALANCED ELECTROLYTES pH 7.4 solution for infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>0</t>
@@ -17743,8 +18167,16 @@
           <t>0421027432-090-658261410724</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CoDICERAN 16/12.5 film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>CoDICERAN 16/12.5 film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>0</t>
@@ -17942,8 +18374,16 @@
           <t>3691311813-142-201361833572</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HAVRIX</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>HAVRIX detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>0</t>
@@ -18137,8 +18577,16 @@
           <t>2468880575-778-919865263385</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OLANA 10 mg orodispersible tablet</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>OLANA 10 mg orodispersible tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
           <t>0</t>
@@ -18328,8 +18776,16 @@
           <t>2153744701-287-441862785379</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SETININ 200 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>SETININ 200 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>0</t>
@@ -18519,8 +18975,16 @@
           <t>6328255754-257-090116896672</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SETININ 300 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>SETININ 300 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
           <t>0</t>
@@ -19112,8 +19576,16 @@
           <t>4136543137-885-290790924024</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVOFLOXACIN Sandoz 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>LEVOFLOXACIN Sandoz 500 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>0</t>
@@ -19311,8 +19783,16 @@
           <t>3156793743-447-335023579664</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CELEBREX 400 mg capsule</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>CELEBREX 400 mg capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>0</t>
@@ -19912,8 +20392,16 @@
           <t>5260448601-427-242537627003</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CIPRALEX 10 MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>CIPRALEX 10 MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>

--- a/product_upload/packages/30/file.xlsx
+++ b/product_upload/packages/30/file.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20828,7 +20828,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22450,7 +22450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22531,40 +22531,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22644,38 +22649,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>417.39</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-86C9B5D60E7A</t>
         </is>
@@ -22755,38 +22765,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>35.4</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-9EF0235C4100</t>
         </is>
@@ -22866,38 +22881,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>94.64</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-EC81E3B0193E</t>
         </is>
@@ -22977,38 +22997,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>471.62</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-342B48F4AA35</t>
         </is>
@@ -23088,38 +23113,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>34.59</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-4AA56BE3BF4D</t>
         </is>
@@ -23199,38 +23229,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>151.22</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-82A802C0B8F6</t>
         </is>
@@ -23310,38 +23345,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>402.69</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-86FD0504F289</t>
         </is>
@@ -23421,38 +23461,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>481.66</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-F5CDE34768D3</t>
         </is>
@@ -23532,38 +23577,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>229.85</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-50247B87831C</t>
         </is>
@@ -23643,38 +23693,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>43.76</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-C4D1C1A16F0C</t>
         </is>
@@ -23754,38 +23809,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>338.57</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-ACEEA7ECA7BD</t>
         </is>
@@ -23865,38 +23925,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>146.44</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-DA6A1911C1B1</t>
         </is>
@@ -23976,38 +24041,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>169.17</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-8F599BCA96ED</t>
         </is>
@@ -24087,38 +24157,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>251.51</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-BF494B91C53D</t>
         </is>
@@ -24198,38 +24273,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>337.34</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-29CB11AB035A</t>
         </is>
@@ -24309,38 +24389,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>87.18000000000001</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-892F5C7C9A3C</t>
         </is>
@@ -24420,38 +24505,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>465.33</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-EF9F7E369E7C</t>
         </is>
@@ -24531,38 +24621,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>367.01</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-5CDF25FFA7B0</t>
         </is>
@@ -24642,38 +24737,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>241.93</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-48B42B6999BF</t>
         </is>
@@ -24753,38 +24853,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>273.84</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-0E7EB47A0729</t>
         </is>
